--- a/DBHYDRO/Shared_data/DBHYDRO_stations.xlsx
+++ b/DBHYDRO/Shared_data/DBHYDRO_stations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Levine\Documents\Git working\Oyster-Reports\DBHYDRO\Shared_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\Oyster-Reports\DBHYDRO\Shared_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECA35A5F-B586-47B0-A6C9-F02CF9D4670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D14D5D-64D6-4473-A46B-F158B8C3C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6504" yWindow="2556" windowWidth="16404" windowHeight="9420" xr2:uid="{20F16024-ED85-4D8A-B94B-797E22D97A29}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20F16024-ED85-4D8A-B94B-797E22D97A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="49">
   <si>
     <t>Data_Type</t>
   </si>
@@ -62,27 +62,18 @@
     <t>SL-S</t>
   </si>
   <si>
-    <t>S80S</t>
-  </si>
-  <si>
     <t>DJ238</t>
   </si>
   <si>
     <t>SL-N_Golf</t>
   </si>
   <si>
-    <t>S97S</t>
-  </si>
-  <si>
     <t>JW225</t>
   </si>
   <si>
     <t>SL-N_Fork</t>
   </si>
   <si>
-    <t>S49S</t>
-  </si>
-  <si>
     <t>SL-N</t>
   </si>
   <si>
@@ -101,9 +92,6 @@
     <t>LX-S</t>
   </si>
   <si>
-    <t>S46S</t>
-  </si>
-  <si>
     <t>00295</t>
   </si>
   <si>
@@ -116,10 +104,85 @@
     <t>DJ237</t>
   </si>
   <si>
-    <t>S79S</t>
-  </si>
-  <si>
     <t>CR</t>
+  </si>
+  <si>
+    <t>LNHRT</t>
+  </si>
+  <si>
+    <t>LW</t>
+  </si>
+  <si>
+    <t>S44</t>
+  </si>
+  <si>
+    <t>91602</t>
+  </si>
+  <si>
+    <t>S41</t>
+  </si>
+  <si>
+    <t>S155</t>
+  </si>
+  <si>
+    <t>91601</t>
+  </si>
+  <si>
+    <t>HR1</t>
+  </si>
+  <si>
+    <t>F9558</t>
+  </si>
+  <si>
+    <t>04013</t>
+  </si>
+  <si>
+    <t>CCORAL</t>
+  </si>
+  <si>
+    <t>PS984</t>
+  </si>
+  <si>
+    <t>UO831</t>
+  </si>
+  <si>
+    <t>MARKH</t>
+  </si>
+  <si>
+    <t>MARKHA</t>
+  </si>
+  <si>
+    <t>88201</t>
+  </si>
+  <si>
+    <t>88197</t>
+  </si>
+  <si>
+    <t>WZ158</t>
+  </si>
+  <si>
+    <t>Sali</t>
+  </si>
+  <si>
+    <t>H2OT</t>
+  </si>
+  <si>
+    <t>Scond</t>
+  </si>
+  <si>
+    <t>S80</t>
+  </si>
+  <si>
+    <t>S97</t>
+  </si>
+  <si>
+    <t>S49</t>
+  </si>
+  <si>
+    <t>S46</t>
+  </si>
+  <si>
+    <t>S79</t>
   </si>
 </sst>
 </file>
@@ -501,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1512136C-6355-400C-9683-C3E596F04973}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -532,10 +595,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -546,13 +609,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -563,13 +626,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -580,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -594,16 +657,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -611,16 +674,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -628,16 +691,220 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/DBHYDRO/Shared_data/DBHYDRO_stations.xlsx
+++ b/DBHYDRO/Shared_data/DBHYDRO_stations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\Oyster-Reports\DBHYDRO\Shared_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D14D5D-64D6-4473-A46B-F158B8C3C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A40A472-DF20-4F20-979D-3F157F5C3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20F16024-ED85-4D8A-B94B-797E22D97A29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20F16024-ED85-4D8A-B94B-797E22D97A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
   <si>
     <t>Data_Type</t>
   </si>
@@ -183,6 +183,36 @@
   </si>
   <si>
     <t>S79</t>
+  </si>
+  <si>
+    <t>91404</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>LWL20</t>
+  </si>
+  <si>
+    <t>WZ743</t>
+  </si>
+  <si>
+    <t>Turb</t>
+  </si>
+  <si>
+    <t>WZ733</t>
+  </si>
+  <si>
+    <t>LWL19</t>
+  </si>
+  <si>
+    <t>39483</t>
+  </si>
+  <si>
+    <t>39336</t>
+  </si>
+  <si>
+    <t>AM024</t>
   </si>
 </sst>
 </file>
@@ -564,10 +594,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1512136C-6355-400C-9683-C3E596F04973}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -584,7 +614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -601,7 +631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -618,7 +648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -635,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -652,7 +682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -669,7 +699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -686,7 +716,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -703,7 +733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -720,7 +750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -737,7 +767,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -754,7 +784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -768,10 +798,10 @@
         <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -788,7 +818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -805,7 +835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -822,7 +852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -839,7 +869,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -856,7 +886,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -873,7 +903,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -890,7 +920,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -905,6 +935,91 @@
       </c>
       <c r="E20" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
